--- a/DOM/AFOLU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
+++ b/DOM/AFOLU/A1_Outputs/A-O_Demand_COMPLETED.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="176">
   <si>
     <t>Demand/Share</t>
   </si>
@@ -274,12 +274,12 @@
     <t>Techs_SUV</t>
   </si>
   <si>
+    <t>Techs_Taxi</t>
+  </si>
+  <si>
     <t>E6TDPASPUB</t>
   </si>
   <si>
-    <t>Techs_Taxi</t>
-  </si>
-  <si>
     <t>Techs_Buses_Pub</t>
   </si>
   <si>
@@ -316,6 +316,18 @@
     <t>E6TRNOMOT</t>
   </si>
   <si>
+    <t>E5CAMFOR</t>
+  </si>
+  <si>
+    <t>E5CAMCUL</t>
+  </si>
+  <si>
+    <t>E5CAMPAS</t>
+  </si>
+  <si>
+    <t>E5CAMASENTA</t>
+  </si>
+  <si>
     <t>Demand Agriculture Rice</t>
   </si>
   <si>
@@ -439,12 +451,12 @@
     <t>Jeep</t>
   </si>
   <si>
+    <t>Taxi Conchos</t>
+  </si>
+  <si>
     <t>Transport Demand - Passenger Public</t>
   </si>
   <si>
-    <t>Taxi Conchos</t>
-  </si>
-  <si>
     <t>Bus Public</t>
   </si>
   <si>
@@ -479,6 +491,18 @@
   </si>
   <si>
     <t>Transport Demand non motorized reductions</t>
+  </si>
+  <si>
+    <t>Tierras convertidas en tierras forestales</t>
+  </si>
+  <si>
+    <t>Tierras de cultivo</t>
+  </si>
+  <si>
+    <t>Pastizales</t>
+  </si>
+  <si>
+    <t>Asentamientos</t>
   </si>
   <si>
     <t>not needed</t>
@@ -875,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AP90"/>
+  <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:42">
@@ -1017,16 +1041,16 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1142,16 +1166,16 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1267,16 +1291,16 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G4" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1392,16 +1416,16 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G5" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1517,16 +1541,16 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1642,16 +1666,16 @@
         <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G7" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1675,85 +1699,85 @@
         <v>0.0027</v>
       </c>
       <c r="O7">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="P7">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="Q7">
-        <v>0.0029</v>
+        <v>0.0027</v>
       </c>
       <c r="R7">
-        <v>0.003</v>
+        <v>0.0027</v>
       </c>
       <c r="S7">
-        <v>0.0031</v>
+        <v>0.0027</v>
       </c>
       <c r="T7">
-        <v>0.0032</v>
+        <v>0.0027</v>
       </c>
       <c r="U7">
-        <v>0.0033</v>
+        <v>0.0027</v>
       </c>
       <c r="V7">
-        <v>0.0034</v>
+        <v>0.0027</v>
       </c>
       <c r="W7">
-        <v>0.0035</v>
+        <v>0.0027</v>
       </c>
       <c r="X7">
-        <v>0.0035</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7">
-        <v>0.0036</v>
+        <v>0.0027</v>
       </c>
       <c r="Z7">
-        <v>0.0037</v>
+        <v>0.0027</v>
       </c>
       <c r="AA7">
-        <v>0.0038</v>
+        <v>0.0027</v>
       </c>
       <c r="AB7">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="AC7">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="AD7">
-        <v>0.004</v>
+        <v>0.0027</v>
       </c>
       <c r="AE7">
-        <v>0.0041</v>
+        <v>0.0027</v>
       </c>
       <c r="AF7">
-        <v>0.0042</v>
+        <v>0.0027</v>
       </c>
       <c r="AG7">
-        <v>0.0042</v>
+        <v>0.0027</v>
       </c>
       <c r="AH7">
-        <v>0.0043</v>
+        <v>0.0027</v>
       </c>
       <c r="AI7">
-        <v>0.0044</v>
+        <v>0.0027</v>
       </c>
       <c r="AJ7">
-        <v>0.0044</v>
+        <v>0.0027</v>
       </c>
       <c r="AK7">
-        <v>0.0045</v>
+        <v>0.0027</v>
       </c>
       <c r="AL7">
-        <v>0.0045</v>
+        <v>0.0027</v>
       </c>
       <c r="AM7">
-        <v>0.0046</v>
+        <v>0.0027</v>
       </c>
       <c r="AN7">
-        <v>0.0046</v>
+        <v>0.0027</v>
       </c>
       <c r="AO7">
-        <v>0.0047</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="8" spans="1:42">
@@ -1767,16 +1791,16 @@
         <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G8" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1892,16 +1916,16 @@
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G9" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2017,16 +2041,16 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G10" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2142,16 +2166,16 @@
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G11" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2267,16 +2291,16 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2392,16 +2416,16 @@
         <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F13" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G13" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2517,22 +2541,22 @@
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G14" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>7.9675</v>
+        <v>7.96</v>
       </c>
       <c r="J14">
         <v>16.889</v>
@@ -2642,16 +2666,16 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G15" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2672,88 +2696,88 @@
         <v>7.1027</v>
       </c>
       <c r="N15">
-        <v>7.2516</v>
+        <v>7.0819</v>
       </c>
       <c r="O15">
-        <v>7.5971</v>
+        <v>7.3414</v>
       </c>
       <c r="P15">
-        <v>7.948</v>
+        <v>7.6022</v>
       </c>
       <c r="Q15">
-        <v>8.2836</v>
+        <v>7.8492</v>
       </c>
       <c r="R15">
-        <v>8.6281</v>
+        <v>8.100300000000001</v>
       </c>
       <c r="S15">
-        <v>8.9975</v>
+        <v>8.367100000000001</v>
       </c>
       <c r="T15">
-        <v>9.3573</v>
+        <v>8.6244</v>
       </c>
       <c r="U15">
-        <v>9.7193</v>
+        <v>8.8812</v>
       </c>
       <c r="V15">
-        <v>10.0511</v>
+        <v>9.1144</v>
       </c>
       <c r="W15">
-        <v>10.3922</v>
+        <v>9.3523</v>
       </c>
       <c r="X15">
-        <v>10.743</v>
+        <v>9.5952</v>
       </c>
       <c r="Y15">
-        <v>11.1036</v>
+        <v>9.8429</v>
       </c>
       <c r="Z15">
-        <v>11.4742</v>
+        <v>10.0956</v>
       </c>
       <c r="AA15">
-        <v>11.7899</v>
+        <v>10.3093</v>
       </c>
       <c r="AB15">
-        <v>12.1128</v>
+        <v>10.5265</v>
       </c>
       <c r="AC15">
-        <v>12.443</v>
+        <v>10.7472</v>
       </c>
       <c r="AD15">
-        <v>12.7807</v>
+        <v>10.9716</v>
       </c>
       <c r="AE15">
-        <v>13.126</v>
+        <v>11.1997</v>
       </c>
       <c r="AF15">
-        <v>13.4088</v>
+        <v>11.3852</v>
       </c>
       <c r="AG15">
-        <v>13.6966</v>
+        <v>11.5732</v>
       </c>
       <c r="AH15">
-        <v>13.9896</v>
+        <v>11.7637</v>
       </c>
       <c r="AI15">
-        <v>14.2877</v>
+        <v>11.9566</v>
       </c>
       <c r="AJ15">
-        <v>14.5912</v>
+        <v>12.1519</v>
       </c>
       <c r="AK15">
-        <v>14.8283</v>
+        <v>12.3038</v>
       </c>
       <c r="AL15">
-        <v>15.0687</v>
+        <v>12.4572</v>
       </c>
       <c r="AM15">
-        <v>15.3123</v>
+        <v>12.6122</v>
       </c>
       <c r="AN15">
-        <v>15.5592</v>
+        <v>12.7686</v>
       </c>
       <c r="AO15">
-        <v>15.8093</v>
+        <v>12.9265</v>
       </c>
     </row>
     <row r="16" spans="1:42">
@@ -2767,16 +2791,16 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F16" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G16" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2892,22 +2916,22 @@
         <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G17" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>7.1088</v>
+        <v>4.0556</v>
       </c>
       <c r="J17">
         <v>9.754799999999999</v>
@@ -3017,16 +3041,16 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F18" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G18" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -3142,16 +3166,16 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F19" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G19" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -3267,22 +3291,22 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F20" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G20" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.1959</v>
       </c>
       <c r="J20">
         <v>0.079</v>
@@ -3392,16 +3416,16 @@
         <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G21" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3422,88 +3446,88 @@
         <v>18.9055</v>
       </c>
       <c r="N21">
-        <v>19.1846</v>
+        <v>18.9055</v>
       </c>
       <c r="O21">
-        <v>19.9851</v>
+        <v>18.9055</v>
       </c>
       <c r="P21">
-        <v>20.7936</v>
+        <v>18.9055</v>
       </c>
       <c r="Q21">
-        <v>21.5626</v>
+        <v>18.9055</v>
       </c>
       <c r="R21">
-        <v>22.348</v>
+        <v>18.9055</v>
       </c>
       <c r="S21">
-        <v>23.186</v>
+        <v>18.9055</v>
       </c>
       <c r="T21">
-        <v>23.9981</v>
+        <v>18.9055</v>
       </c>
       <c r="U21">
-        <v>24.8114</v>
+        <v>18.9055</v>
       </c>
       <c r="V21">
-        <v>25.5532</v>
+        <v>18.9055</v>
       </c>
       <c r="W21">
-        <v>26.3128</v>
+        <v>18.9055</v>
       </c>
       <c r="X21">
-        <v>27.0907</v>
+        <v>18.9055</v>
       </c>
       <c r="Y21">
-        <v>27.8871</v>
+        <v>18.9055</v>
       </c>
       <c r="Z21">
-        <v>28.7024</v>
+        <v>18.9055</v>
       </c>
       <c r="AA21">
-        <v>29.394</v>
+        <v>18.9055</v>
       </c>
       <c r="AB21">
-        <v>30.099</v>
+        <v>18.9055</v>
       </c>
       <c r="AC21">
-        <v>30.8178</v>
+        <v>18.9055</v>
       </c>
       <c r="AD21">
-        <v>31.5503</v>
+        <v>18.9055</v>
       </c>
       <c r="AE21">
-        <v>32.297</v>
+        <v>18.9055</v>
       </c>
       <c r="AF21">
-        <v>32.9063</v>
+        <v>18.9055</v>
       </c>
       <c r="AG21">
-        <v>33.525</v>
+        <v>18.9055</v>
       </c>
       <c r="AH21">
-        <v>34.1531</v>
+        <v>18.9055</v>
       </c>
       <c r="AI21">
-        <v>34.7906</v>
+        <v>18.9055</v>
       </c>
       <c r="AJ21">
-        <v>35.4378</v>
+        <v>18.9055</v>
       </c>
       <c r="AK21">
-        <v>35.9423</v>
+        <v>18.9055</v>
       </c>
       <c r="AL21">
-        <v>36.4526</v>
+        <v>18.9055</v>
       </c>
       <c r="AM21">
-        <v>36.9687</v>
+        <v>18.9055</v>
       </c>
       <c r="AN21">
-        <v>37.4907</v>
+        <v>18.9055</v>
       </c>
       <c r="AO21">
-        <v>38.0187</v>
+        <v>18.9055</v>
       </c>
     </row>
     <row r="22" spans="1:41">
@@ -3517,16 +3541,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G22" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3642,22 +3666,22 @@
         <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G23" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.6377</v>
       </c>
       <c r="J23">
         <v>1.1363</v>
@@ -3767,22 +3791,22 @@
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G24" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>0.3463</v>
       </c>
       <c r="J24">
         <v>0.6405999999999999</v>
@@ -3892,16 +3916,16 @@
         <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G25" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -4017,16 +4041,16 @@
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G26" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -4142,16 +4166,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F27" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G27" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -4267,16 +4291,16 @@
         <v>37</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -4392,16 +4416,16 @@
         <v>38</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E29" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G29" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -4517,16 +4541,16 @@
         <v>39</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G30" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -4642,16 +4666,16 @@
         <v>40</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E31" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G31" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -4767,16 +4791,16 @@
         <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -4892,16 +4916,16 @@
         <v>42</v>
       </c>
       <c r="D33" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G33" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -5017,16 +5041,16 @@
         <v>43</v>
       </c>
       <c r="D34" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G34" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -5142,16 +5166,16 @@
         <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E35" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F35" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G35" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -5264,19 +5288,19 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E36" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F36" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G36" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -5389,19 +5413,19 @@
         <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F37" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G37" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -5514,19 +5538,19 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E38" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G38" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -5639,19 +5663,19 @@
         <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F39" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G39" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -5764,19 +5788,19 @@
         <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D40" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E40" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G40" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -5889,19 +5913,19 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F41" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G41" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -6014,19 +6038,19 @@
         <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G42" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -6139,19 +6163,19 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F43" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G43" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -6264,19 +6288,19 @@
         <v>53</v>
       </c>
       <c r="C44" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F44" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G44" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -6389,19 +6413,19 @@
         <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -6514,19 +6538,19 @@
         <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E46" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -6639,19 +6663,19 @@
         <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -6764,19 +6788,19 @@
         <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D48" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E48" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F48" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -6889,19 +6913,19 @@
         <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E49" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F49" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G49" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -7014,19 +7038,19 @@
         <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E50" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G50" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -7139,19 +7163,19 @@
         <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D51" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E51" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F51" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G51" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -7264,19 +7288,19 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F52" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G52" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -7389,19 +7413,19 @@
         <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E53" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G53" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -7514,19 +7538,19 @@
         <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E54" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F54" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G54" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -7639,19 +7663,19 @@
         <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E55" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F55" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G55" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -7764,19 +7788,19 @@
         <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D56" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E56" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G56" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -7889,19 +7913,19 @@
         <v>66</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E57" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F57" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G57" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -8014,19 +8038,19 @@
         <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F58" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G58" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -8139,19 +8163,19 @@
         <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D59" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E59" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F59" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G59" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -8264,19 +8288,19 @@
         <v>69</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E60" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F60" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G60" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -8389,19 +8413,19 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D61" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F61" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G61" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -8514,19 +8538,19 @@
         <v>71</v>
       </c>
       <c r="C62" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E62" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F62" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G62" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -8639,19 +8663,19 @@
         <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E63" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F63" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G63" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -8764,19 +8788,19 @@
         <v>73</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D64" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F64" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G64" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -8889,19 +8913,19 @@
         <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D65" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E65" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F65" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G65" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -9014,19 +9038,19 @@
         <v>75</v>
       </c>
       <c r="C66" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E66" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F66" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G66" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -9139,19 +9163,19 @@
         <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D67" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G67" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -9264,19 +9288,19 @@
         <v>77</v>
       </c>
       <c r="C68" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D68" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F68" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G68" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -9389,19 +9413,19 @@
         <v>78</v>
       </c>
       <c r="C69" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E69" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F69" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G69" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -9514,19 +9538,19 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E70" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F70" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G70" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -9639,19 +9663,19 @@
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D71" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E71" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F71" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G71" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -9764,19 +9788,19 @@
         <v>81</v>
       </c>
       <c r="C72" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D72" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G72" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -9889,121 +9913,121 @@
         <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D73" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G73" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H73" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I73">
-        <v>59.7859</v>
+        <v>43.2142</v>
       </c>
       <c r="J73">
-        <v>62.9502</v>
+        <v>45.5014</v>
       </c>
       <c r="K73">
-        <v>58.197</v>
+        <v>42.0657</v>
       </c>
       <c r="L73">
-        <v>65.7021</v>
+        <v>47.4906</v>
       </c>
       <c r="M73">
-        <v>69.89870000000001</v>
+        <v>50.5239</v>
       </c>
       <c r="N73">
-        <v>70.93089999999999</v>
+        <v>51.27</v>
       </c>
       <c r="O73">
-        <v>73.217</v>
+        <v>52.9225</v>
       </c>
       <c r="P73">
-        <v>75.50490000000001</v>
+        <v>54.5762</v>
       </c>
       <c r="Q73">
-        <v>77.6621</v>
+        <v>56.1354</v>
       </c>
       <c r="R73">
-        <v>79.8471</v>
+        <v>57.7148</v>
       </c>
       <c r="S73">
-        <v>82.1601</v>
+        <v>59.3866</v>
       </c>
       <c r="T73">
-        <v>84.3828</v>
+        <v>60.9932</v>
       </c>
       <c r="U73">
-        <v>86.592</v>
+        <v>62.5901</v>
       </c>
       <c r="V73">
-        <v>88.5917</v>
+        <v>64.0355</v>
       </c>
       <c r="W73">
-        <v>90.62609999999999</v>
+        <v>65.506</v>
       </c>
       <c r="X73">
-        <v>92.6955</v>
+        <v>67.0018</v>
       </c>
       <c r="Y73">
-        <v>94.8005</v>
+        <v>68.52330000000001</v>
       </c>
       <c r="Z73">
-        <v>96.9413</v>
+        <v>70.07080000000001</v>
       </c>
       <c r="AA73">
-        <v>98.7457</v>
+        <v>71.375</v>
       </c>
       <c r="AB73">
-        <v>100.5754</v>
+        <v>72.69750000000001</v>
       </c>
       <c r="AC73">
-        <v>102.4305</v>
+        <v>74.0384</v>
       </c>
       <c r="AD73">
-        <v>104.3114</v>
+        <v>75.398</v>
       </c>
       <c r="AE73">
-        <v>106.2182</v>
+        <v>76.7762</v>
       </c>
       <c r="AF73">
-        <v>107.7663</v>
+        <v>77.8952</v>
       </c>
       <c r="AG73">
-        <v>109.3314</v>
+        <v>79.0265</v>
       </c>
       <c r="AH73">
-        <v>110.9136</v>
+        <v>80.17010000000001</v>
       </c>
       <c r="AI73">
-        <v>112.513</v>
+        <v>81.3262</v>
       </c>
       <c r="AJ73">
-        <v>114.1298</v>
+        <v>82.4949</v>
       </c>
       <c r="AK73">
-        <v>115.3847</v>
+        <v>83.402</v>
       </c>
       <c r="AL73">
-        <v>116.6501</v>
+        <v>84.31659999999999</v>
       </c>
       <c r="AM73">
-        <v>117.9259</v>
+        <v>85.23869999999999</v>
       </c>
       <c r="AN73">
-        <v>119.2122</v>
+        <v>86.16849999999999</v>
       </c>
       <c r="AO73">
-        <v>120.5091</v>
+        <v>87.10590000000001</v>
       </c>
     </row>
     <row r="74" spans="1:42">
@@ -10014,124 +10038,124 @@
         <v>83</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D74">
-        <v>1045414</v>
+        <v>881250</v>
       </c>
       <c r="E74">
         <v>1.5</v>
       </c>
       <c r="F74">
-        <v>14773</v>
+        <v>7500</v>
       </c>
       <c r="G74" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H74" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I74">
-        <v>15.4447</v>
+        <v>6.6094</v>
       </c>
       <c r="J74">
-        <v>16.2621</v>
+        <v>6.9587</v>
       </c>
       <c r="K74">
-        <v>15.0342</v>
+        <v>6.4332</v>
       </c>
       <c r="L74">
-        <v>16.973</v>
+        <v>7.2629</v>
       </c>
       <c r="M74">
-        <v>18.0572</v>
+        <v>7.7268</v>
       </c>
       <c r="N74">
-        <v>18.3238</v>
+        <v>7.8409</v>
       </c>
       <c r="O74">
-        <v>18.9144</v>
+        <v>8.0936</v>
       </c>
       <c r="P74">
-        <v>19.5054</v>
+        <v>8.346500000000001</v>
       </c>
       <c r="Q74">
-        <v>20.0627</v>
+        <v>8.585000000000001</v>
       </c>
       <c r="R74">
-        <v>20.6272</v>
+        <v>8.826499999999999</v>
       </c>
       <c r="S74">
-        <v>21.2247</v>
+        <v>9.0822</v>
       </c>
       <c r="T74">
-        <v>21.7989</v>
+        <v>9.3279</v>
       </c>
       <c r="U74">
-        <v>22.3696</v>
+        <v>9.572100000000001</v>
       </c>
       <c r="V74">
-        <v>22.8862</v>
+        <v>9.793200000000001</v>
       </c>
       <c r="W74">
-        <v>23.4117</v>
+        <v>10.0181</v>
       </c>
       <c r="X74">
-        <v>23.9463</v>
+        <v>10.2468</v>
       </c>
       <c r="Y74">
-        <v>24.4901</v>
+        <v>10.4795</v>
       </c>
       <c r="Z74">
-        <v>25.0432</v>
+        <v>10.7162</v>
       </c>
       <c r="AA74">
-        <v>25.5093</v>
+        <v>10.9156</v>
       </c>
       <c r="AB74">
-        <v>25.982</v>
+        <v>11.1179</v>
       </c>
       <c r="AC74">
-        <v>26.4612</v>
+        <v>11.3229</v>
       </c>
       <c r="AD74">
-        <v>26.9471</v>
+        <v>11.5309</v>
       </c>
       <c r="AE74">
-        <v>27.4397</v>
+        <v>11.7416</v>
       </c>
       <c r="AF74">
-        <v>27.8396</v>
+        <v>11.9128</v>
       </c>
       <c r="AG74">
-        <v>28.2439</v>
+        <v>12.0858</v>
       </c>
       <c r="AH74">
-        <v>28.6527</v>
+        <v>12.2607</v>
       </c>
       <c r="AI74">
-        <v>29.0659</v>
+        <v>12.4375</v>
       </c>
       <c r="AJ74">
-        <v>29.4835</v>
+        <v>12.6162</v>
       </c>
       <c r="AK74">
-        <v>29.8077</v>
+        <v>12.7549</v>
       </c>
       <c r="AL74">
-        <v>30.1346</v>
+        <v>12.8948</v>
       </c>
       <c r="AM74">
-        <v>30.4642</v>
+        <v>13.0358</v>
       </c>
       <c r="AN74">
-        <v>30.7965</v>
+        <v>13.178</v>
       </c>
       <c r="AO74">
-        <v>31.1315</v>
+        <v>13.3214</v>
       </c>
       <c r="AP74" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:42">
@@ -10142,124 +10166,124 @@
         <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D75">
-        <v>2874590</v>
+        <v>2398511</v>
       </c>
       <c r="E75">
         <v>1.1</v>
       </c>
       <c r="F75">
-        <v>7327</v>
+        <v>10500</v>
       </c>
       <c r="G75" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H75" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I75">
-        <v>21.0609</v>
+        <v>25.1844</v>
       </c>
       <c r="J75">
-        <v>22.1756</v>
+        <v>26.519</v>
       </c>
       <c r="K75">
-        <v>20.5012</v>
+        <v>24.5167</v>
       </c>
       <c r="L75">
-        <v>23.1451</v>
+        <v>27.6784</v>
       </c>
       <c r="M75">
-        <v>24.6234</v>
+        <v>29.4462</v>
       </c>
       <c r="N75">
-        <v>24.987</v>
+        <v>29.8811</v>
       </c>
       <c r="O75">
-        <v>25.7924</v>
+        <v>30.8442</v>
       </c>
       <c r="P75">
-        <v>26.5983</v>
+        <v>31.808</v>
       </c>
       <c r="Q75">
-        <v>27.3582</v>
+        <v>32.7167</v>
       </c>
       <c r="R75">
-        <v>28.128</v>
+        <v>33.6372</v>
       </c>
       <c r="S75">
-        <v>28.9428</v>
+        <v>34.6116</v>
       </c>
       <c r="T75">
-        <v>29.7258</v>
+        <v>35.5479</v>
       </c>
       <c r="U75">
-        <v>30.504</v>
+        <v>36.4786</v>
       </c>
       <c r="V75">
-        <v>31.2084</v>
+        <v>37.3211</v>
       </c>
       <c r="W75">
-        <v>31.9251</v>
+        <v>38.1781</v>
       </c>
       <c r="X75">
-        <v>32.6541</v>
+        <v>39.0499</v>
       </c>
       <c r="Y75">
-        <v>33.3956</v>
+        <v>39.9366</v>
       </c>
       <c r="Z75">
-        <v>34.1498</v>
+        <v>40.8385</v>
       </c>
       <c r="AA75">
-        <v>34.7854</v>
+        <v>41.5986</v>
       </c>
       <c r="AB75">
-        <v>35.43</v>
+        <v>42.3694</v>
       </c>
       <c r="AC75">
-        <v>36.0835</v>
+        <v>43.1509</v>
       </c>
       <c r="AD75">
-        <v>36.7461</v>
+        <v>43.9433</v>
       </c>
       <c r="AE75">
-        <v>37.4178</v>
+        <v>44.7466</v>
       </c>
       <c r="AF75">
-        <v>37.9631</v>
+        <v>45.3987</v>
       </c>
       <c r="AG75">
-        <v>38.5145</v>
+        <v>46.0581</v>
       </c>
       <c r="AH75">
-        <v>39.0718</v>
+        <v>46.7246</v>
       </c>
       <c r="AI75">
-        <v>39.6353</v>
+        <v>47.3984</v>
       </c>
       <c r="AJ75">
-        <v>40.2048</v>
+        <v>48.0795</v>
       </c>
       <c r="AK75">
-        <v>40.6469</v>
+        <v>48.6082</v>
       </c>
       <c r="AL75">
-        <v>41.0926</v>
+        <v>49.1412</v>
       </c>
       <c r="AM75">
-        <v>41.5421</v>
+        <v>49.6787</v>
       </c>
       <c r="AN75">
-        <v>41.9952</v>
+        <v>50.2206</v>
       </c>
       <c r="AO75">
-        <v>42.4521</v>
+        <v>50.7669</v>
       </c>
       <c r="AP75" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:42">
@@ -10270,377 +10294,377 @@
         <v>85</v>
       </c>
       <c r="C76" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D76">
-        <v>569102</v>
+        <v>449918</v>
       </c>
       <c r="E76">
         <v>1.6</v>
       </c>
       <c r="F76">
-        <v>14773</v>
+        <v>7500</v>
       </c>
       <c r="G76" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H76" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I76">
-        <v>8.407400000000001</v>
+        <v>3.3744</v>
       </c>
       <c r="J76">
-        <v>8.852399999999999</v>
+        <v>3.552</v>
       </c>
       <c r="K76">
-        <v>8.183999999999999</v>
+        <v>3.2838</v>
       </c>
       <c r="L76">
-        <v>9.2394</v>
+        <v>3.7072</v>
       </c>
       <c r="M76">
-        <v>9.829499999999999</v>
+        <v>3.944</v>
       </c>
       <c r="N76">
-        <v>9.9747</v>
+        <v>4.0023</v>
       </c>
       <c r="O76">
-        <v>10.2961</v>
+        <v>4.1313</v>
       </c>
       <c r="P76">
-        <v>10.6179</v>
+        <v>4.2604</v>
       </c>
       <c r="Q76">
-        <v>10.9212</v>
+        <v>4.3821</v>
       </c>
       <c r="R76">
-        <v>11.2285</v>
+        <v>4.5054</v>
       </c>
       <c r="S76">
-        <v>11.5538</v>
+        <v>4.6359</v>
       </c>
       <c r="T76">
-        <v>11.8663</v>
+        <v>4.7613</v>
       </c>
       <c r="U76">
-        <v>12.177</v>
+        <v>4.8859</v>
       </c>
       <c r="V76">
-        <v>12.4582</v>
+        <v>4.9988</v>
       </c>
       <c r="W76">
-        <v>12.7443</v>
+        <v>5.1136</v>
       </c>
       <c r="X76">
-        <v>13.0353</v>
+        <v>5.2303</v>
       </c>
       <c r="Y76">
-        <v>13.3313</v>
+        <v>5.3491</v>
       </c>
       <c r="Z76">
-        <v>13.6324</v>
+        <v>5.4699</v>
       </c>
       <c r="AA76">
-        <v>13.8861</v>
+        <v>5.5717</v>
       </c>
       <c r="AB76">
-        <v>14.1434</v>
+        <v>5.6749</v>
       </c>
       <c r="AC76">
-        <v>14.4043</v>
+        <v>5.7796</v>
       </c>
       <c r="AD76">
-        <v>14.6688</v>
+        <v>5.8858</v>
       </c>
       <c r="AE76">
-        <v>14.9369</v>
+        <v>5.9933</v>
       </c>
       <c r="AF76">
-        <v>15.1546</v>
+        <v>6.0807</v>
       </c>
       <c r="AG76">
-        <v>15.3747</v>
+        <v>6.169</v>
       </c>
       <c r="AH76">
-        <v>15.5972</v>
+        <v>6.2583</v>
       </c>
       <c r="AI76">
-        <v>15.8221</v>
+        <v>6.3485</v>
       </c>
       <c r="AJ76">
-        <v>16.0495</v>
+        <v>6.4398</v>
       </c>
       <c r="AK76">
-        <v>16.226</v>
+        <v>6.5106</v>
       </c>
       <c r="AL76">
-        <v>16.4039</v>
+        <v>6.582</v>
       </c>
       <c r="AM76">
-        <v>16.5833</v>
+        <v>6.6539</v>
       </c>
       <c r="AN76">
-        <v>16.7642</v>
+        <v>6.7265</v>
       </c>
       <c r="AO76">
-        <v>16.9466</v>
+        <v>6.7997</v>
       </c>
       <c r="AP76" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" spans="1:42">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
         <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>141</v>
-      </c>
-      <c r="D77" t="s">
-        <v>155</v>
-      </c>
-      <c r="E77" t="s">
-        <v>155</v>
-      </c>
-      <c r="F77" t="s">
-        <v>155</v>
+        <v>145</v>
+      </c>
+      <c r="D77">
+        <v>17630</v>
+      </c>
+      <c r="E77">
+        <v>0.25</v>
+      </c>
+      <c r="F77">
+        <v>45000</v>
       </c>
       <c r="G77" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="H77" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I77">
-        <v>28.9423</v>
+        <v>1.572</v>
       </c>
       <c r="J77">
-        <v>30.4741</v>
+        <v>1.6563</v>
       </c>
       <c r="K77">
-        <v>28.1731</v>
+        <v>1.5312</v>
       </c>
       <c r="L77">
-        <v>31.8063</v>
+        <v>1.7287</v>
       </c>
       <c r="M77">
-        <v>33.8379</v>
+        <v>1.8391</v>
       </c>
       <c r="N77">
-        <v>34.3376</v>
+        <v>1.8662</v>
       </c>
       <c r="O77">
-        <v>35.4443</v>
+        <v>1.9264</v>
       </c>
       <c r="P77">
-        <v>36.5518</v>
+        <v>1.9866</v>
       </c>
       <c r="Q77">
-        <v>37.5962</v>
+        <v>2.0433</v>
       </c>
       <c r="R77">
-        <v>38.6539</v>
+        <v>2.1008</v>
       </c>
       <c r="S77">
-        <v>39.7736</v>
+        <v>2.1617</v>
       </c>
       <c r="T77">
-        <v>40.8496</v>
+        <v>2.2202</v>
       </c>
       <c r="U77">
-        <v>41.9191</v>
+        <v>2.2783</v>
       </c>
       <c r="V77">
-        <v>42.8871</v>
+        <v>2.3309</v>
       </c>
       <c r="W77">
-        <v>43.872</v>
+        <v>2.3844</v>
       </c>
       <c r="X77">
-        <v>44.8738</v>
+        <v>2.4389</v>
       </c>
       <c r="Y77">
-        <v>45.8928</v>
+        <v>2.4942</v>
       </c>
       <c r="Z77">
-        <v>46.9292</v>
+        <v>2.5506</v>
       </c>
       <c r="AA77">
-        <v>47.8027</v>
+        <v>2.5981</v>
       </c>
       <c r="AB77">
-        <v>48.6884</v>
+        <v>2.6462</v>
       </c>
       <c r="AC77">
-        <v>49.5865</v>
+        <v>2.695</v>
       </c>
       <c r="AD77">
-        <v>50.497</v>
+        <v>2.7445</v>
       </c>
       <c r="AE77">
-        <v>51.4201</v>
+        <v>2.7947</v>
       </c>
       <c r="AF77">
-        <v>52.1696</v>
+        <v>2.8354</v>
       </c>
       <c r="AG77">
-        <v>52.9272</v>
+        <v>2.8766</v>
       </c>
       <c r="AH77">
-        <v>53.6932</v>
+        <v>2.9182</v>
       </c>
       <c r="AI77">
-        <v>54.4674</v>
+        <v>2.9603</v>
       </c>
       <c r="AJ77">
-        <v>55.2501</v>
+        <v>3.0028</v>
       </c>
       <c r="AK77">
-        <v>55.8576</v>
+        <v>3.0358</v>
       </c>
       <c r="AL77">
-        <v>56.4702</v>
+        <v>3.0691</v>
       </c>
       <c r="AM77">
-        <v>57.0878</v>
+        <v>3.1027</v>
       </c>
       <c r="AN77">
-        <v>57.7105</v>
+        <v>3.1365</v>
       </c>
       <c r="AO77">
-        <v>58.3383</v>
+        <v>3.1707</v>
+      </c>
+      <c r="AP77" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:42">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
         <v>87</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
-      </c>
-      <c r="D78">
-        <v>16000</v>
-      </c>
-      <c r="E78">
-        <v>0.25</v>
-      </c>
-      <c r="F78">
-        <v>48704</v>
+        <v>146</v>
+      </c>
+      <c r="D78" t="s">
+        <v>163</v>
+      </c>
+      <c r="E78" t="s">
+        <v>163</v>
+      </c>
+      <c r="F78" t="s">
+        <v>163</v>
       </c>
       <c r="G78" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="H78" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="I78">
-        <v>0.7756999999999999</v>
+        <v>21.8086</v>
       </c>
       <c r="J78">
-        <v>0.8167</v>
+        <v>22.9629</v>
       </c>
       <c r="K78">
-        <v>0.755</v>
+        <v>21.229</v>
       </c>
       <c r="L78">
-        <v>0.8524</v>
+        <v>23.9667</v>
       </c>
       <c r="M78">
-        <v>0.9069</v>
+        <v>25.4975</v>
       </c>
       <c r="N78">
-        <v>0.9202</v>
+        <v>25.874</v>
       </c>
       <c r="O78">
-        <v>0.9499</v>
+        <v>26.708</v>
       </c>
       <c r="P78">
-        <v>0.9796</v>
+        <v>27.5425</v>
       </c>
       <c r="Q78">
-        <v>1.0076</v>
+        <v>28.3295</v>
       </c>
       <c r="R78">
-        <v>1.0359</v>
+        <v>29.1265</v>
       </c>
       <c r="S78">
-        <v>1.0659</v>
+        <v>29.9702</v>
       </c>
       <c r="T78">
-        <v>1.0948</v>
+        <v>30.781</v>
       </c>
       <c r="U78">
-        <v>1.1234</v>
+        <v>31.5869</v>
       </c>
       <c r="V78">
-        <v>1.1494</v>
+        <v>32.3163</v>
       </c>
       <c r="W78">
-        <v>1.1758</v>
+        <v>33.0584</v>
       </c>
       <c r="X78">
-        <v>1.2026</v>
+        <v>33.8133</v>
       </c>
       <c r="Y78">
-        <v>1.2299</v>
+        <v>34.5812</v>
       </c>
       <c r="Z78">
-        <v>1.2577</v>
+        <v>35.3621</v>
       </c>
       <c r="AA78">
-        <v>1.2811</v>
+        <v>36.0203</v>
       </c>
       <c r="AB78">
-        <v>1.3048</v>
+        <v>36.6877</v>
       </c>
       <c r="AC78">
-        <v>1.3289</v>
+        <v>37.3644</v>
       </c>
       <c r="AD78">
-        <v>1.3533</v>
+        <v>38.0505</v>
       </c>
       <c r="AE78">
-        <v>1.3781</v>
+        <v>38.7461</v>
       </c>
       <c r="AF78">
-        <v>1.3981</v>
+        <v>39.3108</v>
       </c>
       <c r="AG78">
-        <v>1.4184</v>
+        <v>39.8817</v>
       </c>
       <c r="AH78">
-        <v>1.439</v>
+        <v>40.4589</v>
       </c>
       <c r="AI78">
-        <v>1.4597</v>
+        <v>41.0423</v>
       </c>
       <c r="AJ78">
-        <v>1.4807</v>
+        <v>41.6321</v>
       </c>
       <c r="AK78">
-        <v>1.497</v>
+        <v>42.0899</v>
       </c>
       <c r="AL78">
-        <v>1.5134</v>
+        <v>42.5514</v>
       </c>
       <c r="AM78">
-        <v>1.53</v>
+        <v>43.0168</v>
       </c>
       <c r="AN78">
-        <v>1.5466</v>
+        <v>43.486</v>
       </c>
       <c r="AO78">
-        <v>1.5635</v>
-      </c>
-      <c r="AP78" t="s">
-        <v>167</v>
+        <v>43.9591</v>
       </c>
     </row>
     <row r="79" spans="1:42">
@@ -10651,124 +10675,124 @@
         <v>88</v>
       </c>
       <c r="C79" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D79">
-        <v>10367</v>
+        <v>4960</v>
       </c>
       <c r="E79">
         <v>14.3</v>
       </c>
       <c r="F79">
-        <v>65460</v>
+        <v>33000</v>
       </c>
       <c r="G79" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H79" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I79">
-        <v>0.6786</v>
+        <v>0.1637</v>
       </c>
       <c r="J79">
-        <v>0.7145</v>
+        <v>0.1723</v>
       </c>
       <c r="K79">
-        <v>0.6606</v>
+        <v>0.1593</v>
       </c>
       <c r="L79">
-        <v>0.7458</v>
+        <v>0.1798</v>
       </c>
       <c r="M79">
-        <v>0.7934</v>
+        <v>0.1913</v>
       </c>
       <c r="N79">
-        <v>0.8051</v>
+        <v>0.1941</v>
       </c>
       <c r="O79">
-        <v>0.8310999999999999</v>
+        <v>0.2004</v>
       </c>
       <c r="P79">
-        <v>0.8571</v>
+        <v>0.2067</v>
       </c>
       <c r="Q79">
-        <v>0.8815</v>
+        <v>0.2126</v>
       </c>
       <c r="R79">
-        <v>0.9063</v>
+        <v>0.2186</v>
       </c>
       <c r="S79">
-        <v>0.9326</v>
+        <v>0.2249</v>
       </c>
       <c r="T79">
-        <v>0.9578</v>
+        <v>0.231</v>
       </c>
       <c r="U79">
-        <v>0.9829</v>
+        <v>0.237</v>
       </c>
       <c r="V79">
-        <v>1.0056</v>
+        <v>0.2425</v>
       </c>
       <c r="W79">
-        <v>1.0287</v>
+        <v>0.2481</v>
       </c>
       <c r="X79">
-        <v>1.0522</v>
+        <v>0.2537</v>
       </c>
       <c r="Y79">
-        <v>1.0761</v>
+        <v>0.2595</v>
       </c>
       <c r="Z79">
-        <v>1.1004</v>
+        <v>0.2653</v>
       </c>
       <c r="AA79">
-        <v>1.1209</v>
+        <v>0.2703</v>
       </c>
       <c r="AB79">
-        <v>1.1416</v>
+        <v>0.2753</v>
       </c>
       <c r="AC79">
-        <v>1.1627</v>
+        <v>0.2804</v>
       </c>
       <c r="AD79">
-        <v>1.184</v>
+        <v>0.2855</v>
       </c>
       <c r="AE79">
-        <v>1.2057</v>
+        <v>0.2907</v>
       </c>
       <c r="AF79">
-        <v>1.2232</v>
+        <v>0.295</v>
       </c>
       <c r="AG79">
-        <v>1.241</v>
+        <v>0.2993</v>
       </c>
       <c r="AH79">
-        <v>1.259</v>
+        <v>0.3036</v>
       </c>
       <c r="AI79">
-        <v>1.2771</v>
+        <v>0.308</v>
       </c>
       <c r="AJ79">
-        <v>1.2955</v>
+        <v>0.3124</v>
       </c>
       <c r="AK79">
-        <v>1.3097</v>
+        <v>0.3158</v>
       </c>
       <c r="AL79">
-        <v>1.3241</v>
+        <v>0.3193</v>
       </c>
       <c r="AM79">
-        <v>1.3386</v>
+        <v>0.3228</v>
       </c>
       <c r="AN79">
-        <v>1.3532</v>
+        <v>0.3263</v>
       </c>
       <c r="AO79">
-        <v>1.3679</v>
+        <v>0.3298</v>
       </c>
       <c r="AP79" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:42">
@@ -10779,124 +10803,124 @@
         <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D80">
-        <v>89530</v>
+        <v>95059</v>
       </c>
       <c r="E80">
         <v>4.6365</v>
       </c>
       <c r="F80">
-        <v>45876</v>
+        <v>44000</v>
       </c>
       <c r="G80" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H80" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I80">
-        <v>4.1074</v>
+        <v>4.1826</v>
       </c>
       <c r="J80">
-        <v>4.3248</v>
+        <v>4.4039</v>
       </c>
       <c r="K80">
-        <v>3.9983</v>
+        <v>4.0714</v>
       </c>
       <c r="L80">
-        <v>4.5139</v>
+        <v>4.5964</v>
       </c>
       <c r="M80">
-        <v>4.8022</v>
+        <v>4.89</v>
       </c>
       <c r="N80">
-        <v>4.8731</v>
+        <v>4.9622</v>
       </c>
       <c r="O80">
-        <v>5.0302</v>
+        <v>5.1221</v>
       </c>
       <c r="P80">
-        <v>5.1873</v>
+        <v>5.2822</v>
       </c>
       <c r="Q80">
-        <v>5.3356</v>
+        <v>5.4331</v>
       </c>
       <c r="R80">
-        <v>5.4857</v>
+        <v>5.586</v>
       </c>
       <c r="S80">
-        <v>5.6446</v>
+        <v>5.7478</v>
       </c>
       <c r="T80">
-        <v>5.7973</v>
+        <v>5.9033</v>
       </c>
       <c r="U80">
-        <v>5.949</v>
+        <v>6.0578</v>
       </c>
       <c r="V80">
-        <v>6.0864</v>
+        <v>6.1977</v>
       </c>
       <c r="W80">
-        <v>6.2262</v>
+        <v>6.34</v>
       </c>
       <c r="X80">
-        <v>6.3684</v>
+        <v>6.4848</v>
       </c>
       <c r="Y80">
-        <v>6.513</v>
+        <v>6.6321</v>
       </c>
       <c r="Z80">
-        <v>6.6601</v>
+        <v>6.7818</v>
       </c>
       <c r="AA80">
-        <v>6.784</v>
+        <v>6.9081</v>
       </c>
       <c r="AB80">
-        <v>6.9097</v>
+        <v>7.0361</v>
       </c>
       <c r="AC80">
-        <v>7.0372</v>
+        <v>7.1658</v>
       </c>
       <c r="AD80">
-        <v>7.1664</v>
+        <v>7.2974</v>
       </c>
       <c r="AE80">
-        <v>7.2974</v>
+        <v>7.4308</v>
       </c>
       <c r="AF80">
-        <v>7.4038</v>
+        <v>7.5391</v>
       </c>
       <c r="AG80">
-        <v>7.5113</v>
+        <v>7.6486</v>
       </c>
       <c r="AH80">
-        <v>7.62</v>
+        <v>7.7593</v>
       </c>
       <c r="AI80">
-        <v>7.7299</v>
+        <v>7.8712</v>
       </c>
       <c r="AJ80">
-        <v>7.841</v>
+        <v>7.9843</v>
       </c>
       <c r="AK80">
-        <v>7.9272</v>
+        <v>8.072100000000001</v>
       </c>
       <c r="AL80">
-        <v>8.014099999999999</v>
+        <v>8.160600000000001</v>
       </c>
       <c r="AM80">
-        <v>8.101800000000001</v>
+        <v>8.2499</v>
       </c>
       <c r="AN80">
-        <v>8.190099999999999</v>
+        <v>8.3399</v>
       </c>
       <c r="AO80">
-        <v>8.279199999999999</v>
+        <v>8.4306</v>
       </c>
       <c r="AP80" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:42">
@@ -10907,121 +10931,124 @@
         <v>90</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
-      </c>
-      <c r="D81" t="s">
-        <v>156</v>
-      </c>
-      <c r="E81" t="s">
-        <v>156</v>
-      </c>
-      <c r="F81" t="s">
-        <v>156</v>
+        <v>149</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81">
+        <v>1.75</v>
+      </c>
+      <c r="F81">
+        <v>175200</v>
       </c>
       <c r="G81" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H81" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>0.0712</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>0.0781</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>0.0843</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>0.0897</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>0.0949</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>0.1003</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>0.1053</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>0.1077</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>0.1101</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>0.1126</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>0.1173</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>0.1195</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>0.1217</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>0.1239</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>0.1262</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>0.1299</v>
       </c>
       <c r="AH81">
-        <v>0</v>
+        <v>0.1318</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>0.1337</v>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>0.1356</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>0.1371</v>
       </c>
       <c r="AL81">
-        <v>0</v>
+        <v>0.1386</v>
       </c>
       <c r="AM81">
-        <v>0</v>
+        <v>0.1401</v>
       </c>
       <c r="AN81">
-        <v>0</v>
+        <v>0.1416</v>
       </c>
       <c r="AO81">
-        <v>0</v>
+        <v>0.1432</v>
+      </c>
+      <c r="AP81" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:42">
@@ -11032,121 +11059,124 @@
         <v>91</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
-      </c>
-      <c r="D82" t="s">
-        <v>156</v>
-      </c>
-      <c r="E82" t="s">
-        <v>156</v>
-      </c>
-      <c r="F82" t="s">
-        <v>156</v>
+        <v>150</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82">
+        <v>43.99</v>
+      </c>
+      <c r="F82">
+        <v>849720</v>
       </c>
       <c r="G82" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H82" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>0.0439</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>0.0406</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>0.0487</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>0.0495</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>0.0511</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>0.0527</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>0.0542</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>0.0557</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>0.0573</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>0.0604</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>0.0618</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>0.0646</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>0.0689</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>0.0701</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>0.0727</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>0.0741</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>0.0752</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>0.0762</v>
       </c>
       <c r="AH82">
-        <v>0</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="AI82">
-        <v>0</v>
+        <v>0.0785</v>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>0.0796</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>0.0805</v>
       </c>
       <c r="AL82">
-        <v>0</v>
+        <v>0.0813</v>
       </c>
       <c r="AM82">
-        <v>0</v>
+        <v>0.0822</v>
       </c>
       <c r="AN82">
-        <v>0</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="AO82">
-        <v>0</v>
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AP82" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="83" spans="1:42">
@@ -11157,121 +11187,121 @@
         <v>92</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D83" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E83" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F83" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G83" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H83" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I83">
-        <v>14.556</v>
+        <v>0.5332</v>
       </c>
       <c r="J83">
-        <v>15.3264</v>
+        <v>0.5615</v>
       </c>
       <c r="K83">
-        <v>14.1691</v>
+        <v>0.5191</v>
       </c>
       <c r="L83">
-        <v>15.9964</v>
+        <v>0.586</v>
       </c>
       <c r="M83">
-        <v>17.0182</v>
+        <v>0.6234</v>
       </c>
       <c r="N83">
-        <v>17.2695</v>
+        <v>0.6327</v>
       </c>
       <c r="O83">
-        <v>17.8261</v>
+        <v>0.653</v>
       </c>
       <c r="P83">
-        <v>18.3831</v>
+        <v>0.6734</v>
       </c>
       <c r="Q83">
-        <v>18.9083</v>
+        <v>0.6927</v>
       </c>
       <c r="R83">
-        <v>19.4403</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="S83">
-        <v>20.0034</v>
+        <v>0.7328</v>
       </c>
       <c r="T83">
-        <v>20.5446</v>
+        <v>0.7526</v>
       </c>
       <c r="U83">
-        <v>21.0824</v>
+        <v>0.7723</v>
       </c>
       <c r="V83">
-        <v>21.5693</v>
+        <v>0.7902</v>
       </c>
       <c r="W83">
-        <v>22.0646</v>
+        <v>0.8083</v>
       </c>
       <c r="X83">
-        <v>22.5685</v>
+        <v>0.8268</v>
       </c>
       <c r="Y83">
-        <v>23.081</v>
+        <v>0.8456</v>
       </c>
       <c r="Z83">
-        <v>23.6022</v>
+        <v>0.8646</v>
       </c>
       <c r="AA83">
-        <v>24.0415</v>
+        <v>0.8807</v>
       </c>
       <c r="AB83">
-        <v>24.487</v>
+        <v>0.8971</v>
       </c>
       <c r="AC83">
-        <v>24.9386</v>
+        <v>0.9136</v>
       </c>
       <c r="AD83">
-        <v>25.3966</v>
+        <v>0.9304</v>
       </c>
       <c r="AE83">
-        <v>25.8608</v>
+        <v>0.9474</v>
       </c>
       <c r="AF83">
-        <v>26.2377</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="AG83">
-        <v>26.6188</v>
+        <v>0.9752</v>
       </c>
       <c r="AH83">
-        <v>27.004</v>
+        <v>0.9893</v>
       </c>
       <c r="AI83">
-        <v>27.3934</v>
+        <v>1.0035</v>
       </c>
       <c r="AJ83">
-        <v>27.787</v>
+        <v>1.018</v>
       </c>
       <c r="AK83">
-        <v>28.0926</v>
+        <v>1.0291</v>
       </c>
       <c r="AL83">
-        <v>28.4007</v>
+        <v>1.0404</v>
       </c>
       <c r="AM83">
-        <v>28.7113</v>
+        <v>1.0518</v>
       </c>
       <c r="AN83">
-        <v>29.0245</v>
+        <v>1.0633</v>
       </c>
       <c r="AO83">
-        <v>29.3402</v>
+        <v>1.0749</v>
       </c>
     </row>
     <row r="84" spans="1:42">
@@ -11282,124 +11312,124 @@
         <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D84">
-        <v>15550</v>
+        <v>1130</v>
       </c>
       <c r="E84">
         <v>14.3</v>
       </c>
       <c r="F84">
-        <v>65460</v>
+        <v>33000</v>
       </c>
       <c r="G84" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H84" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I84">
-        <v>1.0179</v>
+        <v>0.0373</v>
       </c>
       <c r="J84">
-        <v>1.0718</v>
+        <v>0.0393</v>
       </c>
       <c r="K84">
-        <v>0.9908</v>
+        <v>0.0363</v>
       </c>
       <c r="L84">
-        <v>1.1186</v>
+        <v>0.041</v>
       </c>
       <c r="M84">
-        <v>1.1901</v>
+        <v>0.0436</v>
       </c>
       <c r="N84">
-        <v>1.2077</v>
+        <v>0.0442</v>
       </c>
       <c r="O84">
-        <v>1.2466</v>
+        <v>0.0457</v>
       </c>
       <c r="P84">
-        <v>1.2855</v>
+        <v>0.0471</v>
       </c>
       <c r="Q84">
-        <v>1.3223</v>
+        <v>0.0484</v>
       </c>
       <c r="R84">
-        <v>1.3595</v>
+        <v>0.0498</v>
       </c>
       <c r="S84">
-        <v>1.3988</v>
+        <v>0.0512</v>
       </c>
       <c r="T84">
-        <v>1.4367</v>
+        <v>0.0526</v>
       </c>
       <c r="U84">
-        <v>1.4743</v>
+        <v>0.054</v>
       </c>
       <c r="V84">
-        <v>1.5083</v>
+        <v>0.0553</v>
       </c>
       <c r="W84">
-        <v>1.543</v>
+        <v>0.0565</v>
       </c>
       <c r="X84">
-        <v>1.5782</v>
+        <v>0.0578</v>
       </c>
       <c r="Y84">
-        <v>1.6141</v>
+        <v>0.0591</v>
       </c>
       <c r="Z84">
-        <v>1.6505</v>
+        <v>0.0605</v>
       </c>
       <c r="AA84">
-        <v>1.6812</v>
+        <v>0.0616</v>
       </c>
       <c r="AB84">
-        <v>1.7124</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="AC84">
-        <v>1.744</v>
+        <v>0.0639</v>
       </c>
       <c r="AD84">
-        <v>1.776</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="AE84">
-        <v>1.8084</v>
+        <v>0.0663</v>
       </c>
       <c r="AF84">
-        <v>1.8348</v>
+        <v>0.0672</v>
       </c>
       <c r="AG84">
-        <v>1.8615</v>
+        <v>0.0682</v>
       </c>
       <c r="AH84">
-        <v>1.8884</v>
+        <v>0.0692</v>
       </c>
       <c r="AI84">
-        <v>1.9156</v>
+        <v>0.0702</v>
       </c>
       <c r="AJ84">
-        <v>1.9431</v>
+        <v>0.0712</v>
       </c>
       <c r="AK84">
-        <v>1.9645</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AL84">
-        <v>1.9861</v>
+        <v>0.0728</v>
       </c>
       <c r="AM84">
-        <v>2.0078</v>
+        <v>0.0736</v>
       </c>
       <c r="AN84">
-        <v>2.0297</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="AO84">
-        <v>2.0518</v>
+        <v>0.0752</v>
       </c>
       <c r="AP84" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:42">
@@ -11410,121 +11440,121 @@
         <v>94</v>
       </c>
       <c r="C85" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D85" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E85" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F85" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G85" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H85" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I85">
-        <v>12.511</v>
+        <v>2.3114</v>
       </c>
       <c r="J85">
-        <v>13.1732</v>
+        <v>2.4338</v>
       </c>
       <c r="K85">
-        <v>12.1785</v>
+        <v>2.25</v>
       </c>
       <c r="L85">
-        <v>13.7491</v>
+        <v>2.5402</v>
       </c>
       <c r="M85">
-        <v>14.6272</v>
+        <v>2.7024</v>
       </c>
       <c r="N85">
-        <v>14.8432</v>
+        <v>2.7423</v>
       </c>
       <c r="O85">
-        <v>15.3216</v>
+        <v>2.8307</v>
       </c>
       <c r="P85">
-        <v>15.8004</v>
+        <v>2.9191</v>
       </c>
       <c r="Q85">
-        <v>16.2518</v>
+        <v>3.0026</v>
       </c>
       <c r="R85">
-        <v>16.7091</v>
+        <v>3.087</v>
       </c>
       <c r="S85">
-        <v>17.1931</v>
+        <v>3.1764</v>
       </c>
       <c r="T85">
-        <v>17.6582</v>
+        <v>3.2624</v>
       </c>
       <c r="U85">
-        <v>18.1205</v>
+        <v>3.3478</v>
       </c>
       <c r="V85">
-        <v>18.539</v>
+        <v>3.4251</v>
       </c>
       <c r="W85">
-        <v>18.9647</v>
+        <v>3.5038</v>
       </c>
       <c r="X85">
-        <v>19.3978</v>
+        <v>3.5838</v>
       </c>
       <c r="Y85">
-        <v>19.8383</v>
+        <v>3.6651</v>
       </c>
       <c r="Z85">
-        <v>20.2863</v>
+        <v>3.7479</v>
       </c>
       <c r="AA85">
-        <v>20.6639</v>
+        <v>3.8177</v>
       </c>
       <c r="AB85">
-        <v>21.0467</v>
+        <v>3.8884</v>
       </c>
       <c r="AC85">
-        <v>21.435</v>
+        <v>3.9601</v>
       </c>
       <c r="AD85">
-        <v>21.8286</v>
+        <v>4.0329</v>
       </c>
       <c r="AE85">
-        <v>22.2276</v>
+        <v>4.1066</v>
       </c>
       <c r="AF85">
-        <v>22.5515</v>
+        <v>4.1664</v>
       </c>
       <c r="AG85">
-        <v>22.8791</v>
+        <v>4.2269</v>
       </c>
       <c r="AH85">
-        <v>23.2102</v>
+        <v>4.2881</v>
       </c>
       <c r="AI85">
-        <v>23.5449</v>
+        <v>4.3499</v>
       </c>
       <c r="AJ85">
-        <v>23.8832</v>
+        <v>4.4125</v>
       </c>
       <c r="AK85">
-        <v>24.1458</v>
+        <v>4.461</v>
       </c>
       <c r="AL85">
-        <v>24.4106</v>
+        <v>4.5099</v>
       </c>
       <c r="AM85">
-        <v>24.6776</v>
+        <v>4.5592</v>
       </c>
       <c r="AN85">
-        <v>24.9468</v>
+        <v>4.6089</v>
       </c>
       <c r="AO85">
-        <v>25.2181</v>
+        <v>4.6591</v>
       </c>
     </row>
     <row r="86" spans="1:42">
@@ -11535,124 +11565,124 @@
         <v>95</v>
       </c>
       <c r="C86" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D86">
-        <v>25294</v>
+        <v>23013</v>
       </c>
       <c r="E86">
         <v>11.16</v>
       </c>
       <c r="F86">
-        <v>44321</v>
+        <v>9000</v>
       </c>
       <c r="G86" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H86" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I86">
-        <v>1.1211</v>
+        <v>0.2071</v>
       </c>
       <c r="J86">
-        <v>1.1804</v>
+        <v>0.2181</v>
       </c>
       <c r="K86">
-        <v>1.0913</v>
+        <v>0.2016</v>
       </c>
       <c r="L86">
-        <v>1.232</v>
+        <v>0.2276</v>
       </c>
       <c r="M86">
-        <v>1.3107</v>
+        <v>0.2422</v>
       </c>
       <c r="N86">
-        <v>1.33</v>
+        <v>0.2457</v>
       </c>
       <c r="O86">
-        <v>1.3729</v>
+        <v>0.2536</v>
       </c>
       <c r="P86">
-        <v>1.4158</v>
+        <v>0.2616</v>
       </c>
       <c r="Q86">
-        <v>1.4563</v>
+        <v>0.2691</v>
       </c>
       <c r="R86">
-        <v>1.4972</v>
+        <v>0.2766</v>
       </c>
       <c r="S86">
-        <v>1.5406</v>
+        <v>0.2846</v>
       </c>
       <c r="T86">
-        <v>1.5823</v>
+        <v>0.2923</v>
       </c>
       <c r="U86">
-        <v>1.6237</v>
+        <v>0.3</v>
       </c>
       <c r="V86">
-        <v>1.6612</v>
+        <v>0.3069</v>
       </c>
       <c r="W86">
-        <v>1.6993</v>
+        <v>0.314</v>
       </c>
       <c r="X86">
-        <v>1.7382</v>
+        <v>0.3211</v>
       </c>
       <c r="Y86">
-        <v>1.7776</v>
+        <v>0.3284</v>
       </c>
       <c r="Z86">
-        <v>1.8178</v>
+        <v>0.3358</v>
       </c>
       <c r="AA86">
-        <v>1.8516</v>
+        <v>0.3421</v>
       </c>
       <c r="AB86">
-        <v>1.8859</v>
+        <v>0.3484</v>
       </c>
       <c r="AC86">
-        <v>1.9207</v>
+        <v>0.3548</v>
       </c>
       <c r="AD86">
-        <v>1.956</v>
+        <v>0.3614</v>
       </c>
       <c r="AE86">
-        <v>1.9917</v>
+        <v>0.368</v>
       </c>
       <c r="AF86">
-        <v>2.0207</v>
+        <v>0.3733</v>
       </c>
       <c r="AG86">
-        <v>2.0501</v>
+        <v>0.3788</v>
       </c>
       <c r="AH86">
-        <v>2.0798</v>
+        <v>0.3842</v>
       </c>
       <c r="AI86">
-        <v>2.1098</v>
+        <v>0.3898</v>
       </c>
       <c r="AJ86">
-        <v>2.1401</v>
+        <v>0.3954</v>
       </c>
       <c r="AK86">
-        <v>2.1636</v>
+        <v>0.3997</v>
       </c>
       <c r="AL86">
-        <v>2.1873</v>
+        <v>0.4041</v>
       </c>
       <c r="AM86">
-        <v>2.2113</v>
+        <v>0.4085</v>
       </c>
       <c r="AN86">
-        <v>2.2354</v>
+        <v>0.413</v>
       </c>
       <c r="AO86">
-        <v>2.2597</v>
+        <v>0.4175</v>
       </c>
       <c r="AP86" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:42">
@@ -11663,22 +11693,22 @@
         <v>96</v>
       </c>
       <c r="C87" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D87" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E87" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F87" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G87" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H87" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -11788,121 +11818,121 @@
         <v>97</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D88" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F88" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G88" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H88" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="I88">
-        <v>15.461</v>
+        <v>7.6003</v>
       </c>
       <c r="J88">
-        <v>16.2793</v>
+        <v>8.0025</v>
       </c>
       <c r="K88">
-        <v>15.0501</v>
+        <v>7.3983</v>
       </c>
       <c r="L88">
-        <v>16.991</v>
+        <v>8.352399999999999</v>
       </c>
       <c r="M88">
-        <v>18.0762</v>
+        <v>8.885899999999999</v>
       </c>
       <c r="N88">
-        <v>18.3432</v>
+        <v>9.017099999999999</v>
       </c>
       <c r="O88">
-        <v>18.9344</v>
+        <v>9.307700000000001</v>
       </c>
       <c r="P88">
-        <v>19.526</v>
+        <v>9.598599999999999</v>
       </c>
       <c r="Q88">
-        <v>20.0839</v>
+        <v>9.8728</v>
       </c>
       <c r="R88">
-        <v>20.649</v>
+        <v>10.1506</v>
       </c>
       <c r="S88">
-        <v>21.2471</v>
+        <v>10.4446</v>
       </c>
       <c r="T88">
-        <v>21.8219</v>
+        <v>10.7272</v>
       </c>
       <c r="U88">
-        <v>22.3932</v>
+        <v>11.008</v>
       </c>
       <c r="V88">
-        <v>22.9103</v>
+        <v>11.2622</v>
       </c>
       <c r="W88">
-        <v>23.4365</v>
+        <v>11.5208</v>
       </c>
       <c r="X88">
-        <v>23.9716</v>
+        <v>11.7839</v>
       </c>
       <c r="Y88">
-        <v>24.516</v>
+        <v>12.0515</v>
       </c>
       <c r="Z88">
-        <v>25.0696</v>
+        <v>12.3237</v>
       </c>
       <c r="AA88">
-        <v>25.5363</v>
+        <v>12.553</v>
       </c>
       <c r="AB88">
-        <v>26.0094</v>
+        <v>12.7856</v>
       </c>
       <c r="AC88">
-        <v>26.4892</v>
+        <v>13.0215</v>
       </c>
       <c r="AD88">
-        <v>26.9756</v>
+        <v>13.2606</v>
       </c>
       <c r="AE88">
-        <v>27.4687</v>
+        <v>13.503</v>
       </c>
       <c r="AF88">
-        <v>27.869</v>
+        <v>13.6998</v>
       </c>
       <c r="AG88">
-        <v>28.2738</v>
+        <v>13.8987</v>
       </c>
       <c r="AH88">
-        <v>28.6829</v>
+        <v>14.0999</v>
       </c>
       <c r="AI88">
-        <v>29.0966</v>
+        <v>14.3032</v>
       </c>
       <c r="AJ88">
-        <v>29.5147</v>
+        <v>14.5087</v>
       </c>
       <c r="AK88">
-        <v>29.8392</v>
+        <v>14.6683</v>
       </c>
       <c r="AL88">
-        <v>30.1664</v>
+        <v>14.8291</v>
       </c>
       <c r="AM88">
-        <v>30.4964</v>
+        <v>14.9913</v>
       </c>
       <c r="AN88">
-        <v>30.829</v>
+        <v>15.1548</v>
       </c>
       <c r="AO88">
-        <v>31.1644</v>
+        <v>15.3197</v>
       </c>
     </row>
     <row r="89" spans="1:42">
@@ -11913,124 +11943,124 @@
         <v>98</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D89">
-        <v>477365</v>
+        <v>454019</v>
       </c>
       <c r="E89">
         <v>1.86</v>
       </c>
       <c r="F89">
-        <v>17413</v>
+        <v>9000</v>
       </c>
       <c r="G89" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H89" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="I89">
-        <v>8.3124</v>
+        <v>4.0862</v>
       </c>
       <c r="J89">
-        <v>8.7523</v>
+        <v>4.3024</v>
       </c>
       <c r="K89">
-        <v>8.0915</v>
+        <v>3.9776</v>
       </c>
       <c r="L89">
-        <v>9.1349</v>
+        <v>4.4905</v>
       </c>
       <c r="M89">
-        <v>9.718400000000001</v>
+        <v>4.7774</v>
       </c>
       <c r="N89">
-        <v>9.8619</v>
+        <v>4.8479</v>
       </c>
       <c r="O89">
-        <v>10.1798</v>
+        <v>5.0041</v>
       </c>
       <c r="P89">
-        <v>10.4978</v>
+        <v>5.1605</v>
       </c>
       <c r="Q89">
-        <v>10.7978</v>
+        <v>5.308</v>
       </c>
       <c r="R89">
-        <v>11.1016</v>
+        <v>5.4573</v>
       </c>
       <c r="S89">
-        <v>11.4232</v>
+        <v>5.6154</v>
       </c>
       <c r="T89">
-        <v>11.7322</v>
+        <v>5.7673</v>
       </c>
       <c r="U89">
-        <v>12.0394</v>
+        <v>5.9183</v>
       </c>
       <c r="V89">
-        <v>12.3174</v>
+        <v>6.0549</v>
       </c>
       <c r="W89">
-        <v>12.6003</v>
+        <v>6.194</v>
       </c>
       <c r="X89">
-        <v>12.888</v>
+        <v>6.3354</v>
       </c>
       <c r="Y89">
-        <v>13.1806</v>
+        <v>6.4793</v>
       </c>
       <c r="Z89">
-        <v>13.4783</v>
+        <v>6.6256</v>
       </c>
       <c r="AA89">
-        <v>13.7292</v>
+        <v>6.7489</v>
       </c>
       <c r="AB89">
-        <v>13.9835</v>
+        <v>6.874</v>
       </c>
       <c r="AC89">
-        <v>14.2415</v>
+        <v>7.0008</v>
       </c>
       <c r="AD89">
-        <v>14.503</v>
+        <v>7.1294</v>
       </c>
       <c r="AE89">
-        <v>14.7681</v>
+        <v>7.2597</v>
       </c>
       <c r="AF89">
-        <v>14.9833</v>
+        <v>7.3655</v>
       </c>
       <c r="AG89">
-        <v>15.201</v>
+        <v>7.4724</v>
       </c>
       <c r="AH89">
-        <v>15.4209</v>
+        <v>7.5806</v>
       </c>
       <c r="AI89">
-        <v>15.6433</v>
+        <v>7.6899</v>
       </c>
       <c r="AJ89">
-        <v>15.8681</v>
+        <v>7.8004</v>
       </c>
       <c r="AK89">
-        <v>16.0426</v>
+        <v>7.8862</v>
       </c>
       <c r="AL89">
-        <v>16.2185</v>
+        <v>7.9726</v>
       </c>
       <c r="AM89">
-        <v>16.3959</v>
+        <v>8.059799999999999</v>
       </c>
       <c r="AN89">
-        <v>16.5747</v>
+        <v>8.1477</v>
       </c>
       <c r="AO89">
-        <v>16.7551</v>
+        <v>8.2364</v>
       </c>
       <c r="AP89" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:42">
@@ -12041,372 +12071,624 @@
         <v>99</v>
       </c>
       <c r="C90" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D90" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E90" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F90" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G90" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H90" t="s">
+        <v>173</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
+      <c r="AE90">
+        <v>0</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>0</v>
+      </c>
+      <c r="AH90">
+        <v>0</v>
+      </c>
+      <c r="AI90">
+        <v>0</v>
+      </c>
+      <c r="AJ90">
+        <v>0</v>
+      </c>
+      <c r="AK90">
+        <v>0</v>
+      </c>
+      <c r="AL90">
+        <v>0</v>
+      </c>
+      <c r="AM90">
+        <v>0</v>
+      </c>
+      <c r="AN90">
+        <v>0</v>
+      </c>
+      <c r="AO90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:42">
+      <c r="A91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" t="s">
+        <v>163</v>
+      </c>
+      <c r="E91" t="s">
+        <v>163</v>
+      </c>
+      <c r="F91" t="s">
+        <v>163</v>
+      </c>
+      <c r="G91" t="s">
         <v>165</v>
       </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90">
-        <v>0</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90">
-        <v>0</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
-      <c r="AB90">
-        <v>0</v>
-      </c>
-      <c r="AC90">
-        <v>0</v>
-      </c>
-      <c r="AD90">
-        <v>0</v>
-      </c>
-      <c r="AE90">
-        <v>0</v>
-      </c>
-      <c r="AF90">
-        <v>0</v>
-      </c>
-      <c r="AG90">
-        <v>0</v>
-      </c>
-      <c r="AH90">
-        <v>0</v>
-      </c>
-      <c r="AI90">
-        <v>0</v>
-      </c>
-      <c r="AJ90">
-        <v>0</v>
-      </c>
-      <c r="AK90">
-        <v>0</v>
-      </c>
-      <c r="AL90">
-        <v>0</v>
-      </c>
-      <c r="AM90">
-        <v>0</v>
-      </c>
-      <c r="AN90">
-        <v>0</v>
-      </c>
-      <c r="AO90">
-        <v>0</v>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0.012</v>
+      </c>
+      <c r="J91">
+        <v>0.007</v>
+      </c>
+      <c r="K91">
+        <v>0.022</v>
+      </c>
+      <c r="L91">
+        <v>0.004</v>
+      </c>
+      <c r="M91">
+        <v>0.034</v>
+      </c>
+      <c r="N91">
+        <v>0.034</v>
+      </c>
+      <c r="O91">
+        <v>0.034</v>
+      </c>
+      <c r="P91">
+        <v>0.034</v>
+      </c>
+      <c r="Q91">
+        <v>0.034</v>
+      </c>
+      <c r="R91">
+        <v>0.034</v>
+      </c>
+      <c r="S91">
+        <v>0.034</v>
+      </c>
+      <c r="T91">
+        <v>0.034</v>
+      </c>
+      <c r="U91">
+        <v>0.034</v>
+      </c>
+      <c r="V91">
+        <v>0.034</v>
+      </c>
+      <c r="W91">
+        <v>0.034</v>
+      </c>
+      <c r="X91">
+        <v>0.034</v>
+      </c>
+      <c r="Y91">
+        <v>0.034</v>
+      </c>
+      <c r="Z91">
+        <v>0.034</v>
+      </c>
+      <c r="AA91">
+        <v>0.034</v>
+      </c>
+      <c r="AB91">
+        <v>0.034</v>
+      </c>
+      <c r="AC91">
+        <v>0.034</v>
+      </c>
+      <c r="AD91">
+        <v>0.034</v>
+      </c>
+      <c r="AE91">
+        <v>0.034</v>
+      </c>
+      <c r="AF91">
+        <v>0.034</v>
+      </c>
+      <c r="AG91">
+        <v>0.034</v>
+      </c>
+      <c r="AH91">
+        <v>0.034</v>
+      </c>
+      <c r="AI91">
+        <v>0.034</v>
+      </c>
+      <c r="AJ91">
+        <v>0.034</v>
+      </c>
+      <c r="AK91">
+        <v>0.034</v>
+      </c>
+      <c r="AL91">
+        <v>0.034</v>
+      </c>
+      <c r="AM91">
+        <v>0.034</v>
+      </c>
+      <c r="AN91">
+        <v>0.034</v>
+      </c>
+      <c r="AO91">
+        <v>0.034</v>
+      </c>
+    </row>
+    <row r="92" spans="1:42">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" t="s">
+        <v>160</v>
+      </c>
+      <c r="D92" t="s">
+        <v>163</v>
+      </c>
+      <c r="E92" t="s">
+        <v>163</v>
+      </c>
+      <c r="F92" t="s">
+        <v>163</v>
+      </c>
+      <c r="G92" t="s">
+        <v>165</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0.002</v>
+      </c>
+      <c r="J92">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K92">
+        <v>0.012</v>
+      </c>
+      <c r="L92">
+        <v>0.01</v>
+      </c>
+      <c r="M92">
+        <v>0.016</v>
+      </c>
+      <c r="N92">
+        <v>0.006</v>
+      </c>
+      <c r="O92">
+        <v>0.006</v>
+      </c>
+      <c r="P92">
+        <v>0.006</v>
+      </c>
+      <c r="Q92">
+        <v>0.006</v>
+      </c>
+      <c r="R92">
+        <v>0.006</v>
+      </c>
+      <c r="S92">
+        <v>0.006</v>
+      </c>
+      <c r="T92">
+        <v>0.006</v>
+      </c>
+      <c r="U92">
+        <v>0.005</v>
+      </c>
+      <c r="V92">
+        <v>0.005</v>
+      </c>
+      <c r="W92">
+        <v>0.005</v>
+      </c>
+      <c r="X92">
+        <v>0.005</v>
+      </c>
+      <c r="Y92">
+        <v>0.005</v>
+      </c>
+      <c r="Z92">
+        <v>0.005</v>
+      </c>
+      <c r="AA92">
+        <v>0.005</v>
+      </c>
+      <c r="AB92">
+        <v>0.005</v>
+      </c>
+      <c r="AC92">
+        <v>0.005</v>
+      </c>
+      <c r="AD92">
+        <v>0.005</v>
+      </c>
+      <c r="AE92">
+        <v>0.005</v>
+      </c>
+      <c r="AF92">
+        <v>0.005</v>
+      </c>
+      <c r="AG92">
+        <v>0.005</v>
+      </c>
+      <c r="AH92">
+        <v>0.005</v>
+      </c>
+      <c r="AI92">
+        <v>0.005</v>
+      </c>
+      <c r="AJ92">
+        <v>0.005</v>
+      </c>
+      <c r="AK92">
+        <v>0.005</v>
+      </c>
+      <c r="AL92">
+        <v>0.005</v>
+      </c>
+      <c r="AM92">
+        <v>0.005</v>
+      </c>
+      <c r="AN92">
+        <v>0.005</v>
+      </c>
+      <c r="AO92">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="93" spans="1:42">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" t="s">
+        <v>161</v>
+      </c>
+      <c r="D93" t="s">
+        <v>163</v>
+      </c>
+      <c r="E93" t="s">
+        <v>163</v>
+      </c>
+      <c r="F93" t="s">
+        <v>163</v>
+      </c>
+      <c r="G93" t="s">
+        <v>165</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0.011</v>
+      </c>
+      <c r="J93">
+        <v>0.014</v>
+      </c>
+      <c r="K93">
+        <v>0.022</v>
+      </c>
+      <c r="L93">
+        <v>0.017</v>
+      </c>
+      <c r="M93">
+        <v>0.024</v>
+      </c>
+      <c r="N93">
+        <v>0.027</v>
+      </c>
+      <c r="O93">
+        <v>0.027</v>
+      </c>
+      <c r="P93">
+        <v>0.027</v>
+      </c>
+      <c r="Q93">
+        <v>0.027</v>
+      </c>
+      <c r="R93">
+        <v>0.027</v>
+      </c>
+      <c r="S93">
+        <v>0.027</v>
+      </c>
+      <c r="T93">
+        <v>0.027</v>
+      </c>
+      <c r="U93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="V93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="W93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="X93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Y93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="Z93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AA93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AB93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AC93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AD93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AE93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AF93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AG93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AH93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AI93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AJ93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AK93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AL93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AM93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AN93">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AO93">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:42">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" t="s">
+        <v>162</v>
+      </c>
+      <c r="D94" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" t="s">
+        <v>163</v>
+      </c>
+      <c r="F94" t="s">
+        <v>163</v>
+      </c>
+      <c r="G94" t="s">
+        <v>165</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0.112</v>
+      </c>
+      <c r="J94">
+        <v>0.112</v>
+      </c>
+      <c r="K94">
+        <v>0.112</v>
+      </c>
+      <c r="L94">
+        <v>0.112</v>
+      </c>
+      <c r="M94">
+        <v>0.112</v>
+      </c>
+      <c r="N94">
+        <v>0.112</v>
+      </c>
+      <c r="O94">
+        <v>0.112</v>
+      </c>
+      <c r="P94">
+        <v>0.112</v>
+      </c>
+      <c r="Q94">
+        <v>0.112</v>
+      </c>
+      <c r="R94">
+        <v>0.112</v>
+      </c>
+      <c r="S94">
+        <v>0.112</v>
+      </c>
+      <c r="T94">
+        <v>0.112</v>
+      </c>
+      <c r="U94">
+        <v>0.112</v>
+      </c>
+      <c r="V94">
+        <v>0.112</v>
+      </c>
+      <c r="W94">
+        <v>0.112</v>
+      </c>
+      <c r="X94">
+        <v>0.112</v>
+      </c>
+      <c r="Y94">
+        <v>0.112</v>
+      </c>
+      <c r="Z94">
+        <v>0.112</v>
+      </c>
+      <c r="AA94">
+        <v>0.112</v>
+      </c>
+      <c r="AB94">
+        <v>0.112</v>
+      </c>
+      <c r="AC94">
+        <v>0.112</v>
+      </c>
+      <c r="AD94">
+        <v>0.112</v>
+      </c>
+      <c r="AE94">
+        <v>0.112</v>
+      </c>
+      <c r="AF94">
+        <v>0.112</v>
+      </c>
+      <c r="AG94">
+        <v>0.112</v>
+      </c>
+      <c r="AH94">
+        <v>0.112</v>
+      </c>
+      <c r="AI94">
+        <v>0.112</v>
+      </c>
+      <c r="AJ94">
+        <v>0.112</v>
+      </c>
+      <c r="AK94">
+        <v>0.112</v>
+      </c>
+      <c r="AL94">
+        <v>0.112</v>
+      </c>
+      <c r="AM94">
+        <v>0.112</v>
+      </c>
+      <c r="AN94">
+        <v>0.112</v>
+      </c>
+      <c r="AO94">
+        <v>0.112</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12AB3331-32D4-4AC9-A702-09AE27B914D7}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE20C1C-FFB7-430B-ADF9-C595D374A295}"/>
 </file>